--- a/artfynd/A 32403-2020 artfynd.xlsx
+++ b/artfynd/A 32403-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120767772</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
